--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -1365,6 +1365,126 @@
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
+    <comment ref="AC33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AD33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AF33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AG33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AH33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AI33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AK33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AL33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AM33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AN33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AC34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AD34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AF34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AG34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AH34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AI34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AK34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AL34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AM34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AN34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
@@ -2876,6 +2996,126 @@
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
+      </text>
+    </comment>
+    <comment ref="AC22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AD22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AF22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AG22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AH22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AI22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AK22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AL22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AM22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AN22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AC23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AD23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AF23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AG23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AH23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AI23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AK23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AL23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AM23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AN23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
@@ -4155,7 +4395,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4523,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 20.5, "op_wape_pct": 88.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 420.44, "rev_act": 508.41, "op_pred": 2.4, "op_act": 14.24}, {"q": "2025Q4", "rev_pred": 537.81, "rev_act": 456.95, "op_pred": 3.08, "op_act": 0.26}, {"q": "2026Q1", "rev_pred": 475.16, "rev_act": 618.74, "op_pred": 2.72, "op_act": 4.63}, {"q": "2026Q2", "rev_pred": 478.52, "rev_act": 617.57, "op_pred": 2.74, "op_act": 28.56}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 20.5, "op_wape_pct": 88.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 420.44, "rev_act": 508.41, "op_pred": 2.4, "op_act": 14.24}, {"q": "2025Q4", "rev_pred": 537.81, "rev_act": 456.95, "op_pred": 3.08, "op_act": 0.26}, {"q": "2026Q1", "rev_pred": 475.16, "rev_act": 618.74, "op_pred": 2.72, "op_act": 4.63}, {"q": "2026Q2", "rev_pred": 478.52, "rev_act": 617.57, "op_pred": 2.74, "op_act": 28.56}]}</t>
         </is>
       </c>
     </row>
@@ -8046,18 +8286,38 @@
         <f>IFERROR(subQ!AB22/subQ!AA22-1,"")</f>
         <v/>
       </c>
-      <c r="AC33" s="31" t="n"/>
-      <c r="AD33" s="31" t="n"/>
+      <c r="AC33" s="24" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="AD33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AE33" s="25" t="n"/>
-      <c r="AF33" s="31" t="n"/>
-      <c r="AG33" s="31" t="n"/>
-      <c r="AH33" s="31" t="n"/>
-      <c r="AI33" s="31" t="n"/>
+      <c r="AF33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ33" s="25" t="n"/>
-      <c r="AK33" s="31" t="n"/>
-      <c r="AL33" s="31" t="n"/>
-      <c r="AM33" s="31" t="n"/>
-      <c r="AN33" s="31" t="n"/>
+      <c r="AK33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AO33" s="25" t="n"/>
     </row>
     <row r="34">
@@ -8154,18 +8414,38 @@
         <f>IFERROR(subQ!AB23/subQ!AA23-1,"")</f>
         <v/>
       </c>
-      <c r="AC34" s="31" t="n"/>
-      <c r="AD34" s="31" t="n"/>
+      <c r="AC34" s="24" t="n">
+        <v>0.016611</v>
+      </c>
+      <c r="AD34" s="24" t="n">
+        <v>0.016758</v>
+      </c>
       <c r="AE34" s="25" t="n"/>
-      <c r="AF34" s="31" t="n"/>
-      <c r="AG34" s="31" t="n"/>
-      <c r="AH34" s="31" t="n"/>
-      <c r="AI34" s="31" t="n"/>
+      <c r="AF34" s="24" t="n">
+        <v>0.015185</v>
+      </c>
+      <c r="AG34" s="24" t="n">
+        <v>0.023973</v>
+      </c>
+      <c r="AH34" s="24" t="n">
+        <v>0.015275</v>
+      </c>
+      <c r="AI34" s="24" t="n">
+        <v>0.015434</v>
+      </c>
       <c r="AJ34" s="25" t="n"/>
-      <c r="AK34" s="31" t="n"/>
-      <c r="AL34" s="31" t="n"/>
-      <c r="AM34" s="31" t="n"/>
-      <c r="AN34" s="31" t="n"/>
+      <c r="AK34" s="24" t="n">
+        <v>0.013942</v>
+      </c>
+      <c r="AL34" s="24" t="n">
+        <v>0.022184</v>
+      </c>
+      <c r="AM34" s="24" t="n">
+        <v>0.014191</v>
+      </c>
+      <c r="AN34" s="24" t="n">
+        <v>0.01438</v>
+      </c>
       <c r="AO34" s="25" t="n"/>
     </row>
     <row r="35">
@@ -10097,7 +10377,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12221,8 +12501,15 @@
         <v>107988.29</v>
       </c>
       <c r="U24" s="9" t="n"/>
-      <c r="Z24" s="9" t="n"/>
-      <c r="AB24" s="5" t="n"/>
+      <c r="Y24" s="18" t="n">
+        <v>38800</v>
+      </c>
+      <c r="Z24" s="34" t="n">
+        <v>38800</v>
+      </c>
+      <c r="AB24" s="19" t="n">
+        <v>117391.52</v>
+      </c>
       <c r="AC24" s="10" t="n"/>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
@@ -12268,7 +12555,9 @@
       <c r="P25" s="9" t="n"/>
       <c r="U25" s="9" t="n"/>
       <c r="Z25" s="9" t="n"/>
-      <c r="AB25" s="5" t="n"/>
+      <c r="AB25" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC25" s="10" t="n"/>
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="11" t="n"/>
@@ -12885,7 +13174,9 @@
       </c>
       <c r="U33" s="9" t="n"/>
       <c r="Z33" s="9" t="n"/>
-      <c r="AB33" s="5" t="n"/>
+      <c r="AB33" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
@@ -14184,8 +14475,15 @@
       <c r="X47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n"/>
-      <c r="AB47" s="5" t="n"/>
+      <c r="Y47" s="18" t="n">
+        <v>38800</v>
+      </c>
+      <c r="Z47" s="34" t="n">
+        <v>38800</v>
+      </c>
+      <c r="AB47" s="19" t="n">
+        <v>117391.52</v>
+      </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
       <c r="AE47" s="11" t="n"/>
@@ -14269,8 +14567,15 @@
       <c r="X48" s="18" t="n">
         <v>-33057.29</v>
       </c>
-      <c r="Z48" s="9" t="n"/>
-      <c r="AB48" s="5" t="n"/>
+      <c r="Y48" s="18" t="n">
+        <v>9499.4</v>
+      </c>
+      <c r="Z48" s="34" t="n">
+        <v>9499.4</v>
+      </c>
+      <c r="AB48" s="19" t="n">
+        <v>75369.02</v>
+      </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
       <c r="AE48" s="11" t="n"/>
@@ -18232,7 +18537,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29311,31 +29616,67 @@
         <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(X$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="Y22" s="18" t="n"/>
+      <c r="Y22" s="18">
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(Y$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="Z22" s="34">
-        <f>Y22</f>
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(Z$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="AA22" s="18" t="n"/>
-      <c r="AB22" s="19" t="n"/>
-      <c r="AC22" s="20" t="n"/>
-      <c r="AD22" s="20" t="n"/>
+      <c r="AB22" s="19">
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(AB$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="AC22" s="20">
+        <f>IFERROR(AB22*(1+변수!AC33),"")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="20">
+        <f>IFERROR(AC22*(1+변수!AD33),"")</f>
+        <v/>
+      </c>
       <c r="AE22" s="35">
         <f>AD22</f>
         <v/>
       </c>
-      <c r="AF22" s="20" t="n"/>
-      <c r="AG22" s="20" t="n"/>
-      <c r="AH22" s="20" t="n"/>
-      <c r="AI22" s="20" t="n"/>
+      <c r="AF22" s="20">
+        <f>IFERROR(AD22*(1+변수!AF33),"")</f>
+        <v/>
+      </c>
+      <c r="AG22" s="20">
+        <f>IFERROR(AF22*(1+변수!AG33),"")</f>
+        <v/>
+      </c>
+      <c r="AH22" s="20">
+        <f>IFERROR(AG22*(1+변수!AH33),"")</f>
+        <v/>
+      </c>
+      <c r="AI22" s="20">
+        <f>IFERROR(AH22*(1+변수!AI33),"")</f>
+        <v/>
+      </c>
       <c r="AJ22" s="35">
         <f>AI22</f>
         <v/>
       </c>
-      <c r="AK22" s="20" t="n"/>
-      <c r="AL22" s="20" t="n"/>
-      <c r="AM22" s="20" t="n"/>
-      <c r="AN22" s="20" t="n"/>
+      <c r="AK22" s="20">
+        <f>IFERROR(AI22*(1+변수!AK33),"")</f>
+        <v/>
+      </c>
+      <c r="AL22" s="20">
+        <f>IFERROR(AK22*(1+변수!AL33),"")</f>
+        <v/>
+      </c>
+      <c r="AM22" s="20">
+        <f>IFERROR(AL22*(1+변수!AM33),"")</f>
+        <v/>
+      </c>
+      <c r="AN22" s="20">
+        <f>IFERROR(AM22*(1+변수!AN33),"")</f>
+        <v/>
+      </c>
       <c r="AO22" s="35">
         <f>AN22</f>
         <v/>
@@ -29442,31 +29783,67 @@
         <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(X$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="Y23" s="18" t="n"/>
+      <c r="Y23" s="18">
+        <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(Y$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="Z23" s="34">
-        <f>Y23</f>
+        <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(Z$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="AA23" s="18" t="n"/>
-      <c r="AB23" s="19" t="n"/>
-      <c r="AC23" s="20" t="n"/>
-      <c r="AD23" s="20" t="n"/>
+      <c r="AB23" s="19">
+        <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(AB$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="AC23" s="20">
+        <f>IFERROR(AB23*(1+변수!AC34),"")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="20">
+        <f>IFERROR(AC23*(1+변수!AD34),"")</f>
+        <v/>
+      </c>
       <c r="AE23" s="35">
         <f>AD23</f>
         <v/>
       </c>
-      <c r="AF23" s="20" t="n"/>
-      <c r="AG23" s="20" t="n"/>
-      <c r="AH23" s="20" t="n"/>
-      <c r="AI23" s="20" t="n"/>
+      <c r="AF23" s="20">
+        <f>IFERROR(AD23*(1+변수!AF34),"")</f>
+        <v/>
+      </c>
+      <c r="AG23" s="20">
+        <f>IFERROR(AF23*(1+변수!AG34),"")</f>
+        <v/>
+      </c>
+      <c r="AH23" s="20">
+        <f>IFERROR(AG23*(1+변수!AH34),"")</f>
+        <v/>
+      </c>
+      <c r="AI23" s="20">
+        <f>IFERROR(AH23*(1+변수!AI34),"")</f>
+        <v/>
+      </c>
       <c r="AJ23" s="35">
         <f>AI23</f>
         <v/>
       </c>
-      <c r="AK23" s="20" t="n"/>
-      <c r="AL23" s="20" t="n"/>
-      <c r="AM23" s="20" t="n"/>
-      <c r="AN23" s="20" t="n"/>
+      <c r="AK23" s="20">
+        <f>IFERROR(AI23*(1+변수!AK34),"")</f>
+        <v/>
+      </c>
+      <c r="AL23" s="20">
+        <f>IFERROR(AK23*(1+변수!AL34),"")</f>
+        <v/>
+      </c>
+      <c r="AM23" s="20">
+        <f>IFERROR(AL23*(1+변수!AM34),"")</f>
+        <v/>
+      </c>
+      <c r="AN23" s="20">
+        <f>IFERROR(AM23*(1+변수!AN34),"")</f>
+        <v/>
+      </c>
       <c r="AO23" s="35">
         <f>AN23</f>
         <v/>

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2815</v>
+        <v>2850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2820</v>
+        <v>2830</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2815</v>
+        <v>2850</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03324334354667688</v>
+        <v>0.03324334354667263</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.07700489386235312</v>
+        <v>0.07700489386235108</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6029,7 +6029,7 @@
         <v>4770</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2905</v>
+        <v>3150</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2830</v>
+        <v>2845</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,825원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,810원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2900</v>
+        <v>2990</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2845</v>
+        <v>2875</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2900</v>
+        <v>2990</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,810원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,865원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03324334354667263</v>
+        <v>0.03324334354667688</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.07700489386235108</v>
+        <v>0.07700489386235312</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2990</v>
+        <v>3030</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2875</v>
+        <v>2883</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2990</v>
+        <v>3030</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,865원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,895원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03324334354667688</v>
+        <v>0.03324334354667263</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.07700489386235312</v>
+        <v>0.07700489386235108</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3030</v>
+        <v>2880</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2883</v>
+        <v>2882.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>3030</v>
+        <v>2880</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2880</v>
+        <v>2900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2882.5</v>
+        <v>2882.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2880</v>
+        <v>2900</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,895원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,020원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2900</v>
+        <v>2975</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2882.9</v>
+        <v>2890.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2900</v>
+        <v>2975</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,020원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,850원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2975</v>
+        <v>3010</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2890.6</v>
+        <v>2910</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>2975</v>
+        <v>3010</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,920원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002220_model.xlsx
+++ b/argus/kship/models/002220_model.xlsx
@@ -4099,7 +4099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4970,35 +4970,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5089,35 +5089,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5208,35 +5208,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5327,35 +5327,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5446,35 +5446,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5565,35 +5565,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5684,35 +5684,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5803,35 +5803,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5938,7 +5938,7 @@
         <v>2830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3010</v>
+        <v>2815</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6211,7 +6211,7 @@
         <v>3358.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2910</v>
+        <v>2900</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>3010</v>
+        <v>2815</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,920원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,875원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39711,7 +39711,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="33">
